--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2943" uniqueCount="993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="1014">
   <si>
     <t>task_name</t>
   </si>
@@ -2951,9 +2951,6 @@
     <t>TC_Audit_10</t>
   </si>
   <si>
-    <t>create_assignment</t>
-  </si>
-  <si>
     <t>TC_Audit_11</t>
   </si>
   <si>
@@ -3029,13 +3026,79 @@
     <t>Verify that Assign Questionnaire to Sub Auditee</t>
   </si>
   <si>
-    <t>add_assign_form</t>
-  </si>
-  <si>
     <t>{"email_id" : "bhavani+69@secmark.in"}</t>
   </si>
   <si>
     <t>{"head_of_auditor":"bhavani+69@secmark.in"}</t>
+  </si>
+  <si>
+    <t>TC_Audit_16</t>
+  </si>
+  <si>
+    <t>Verify that Assign Checklist to Sub Auditee</t>
+  </si>
+  <si>
+    <t>{"email_head" : "bhavani+71@secmark.in", "email_subauditee1": "bhavani+89@secmark.in", "email_subauditee2":"bhavani+69@secmark.in"}</t>
+  </si>
+  <si>
+    <t>dash_audit_export_data</t>
+  </si>
+  <si>
+    <t>TC_Audit_17</t>
+  </si>
+  <si>
+    <t>Verify that Dashboard Audit Data Exported Successfully</t>
+  </si>
+  <si>
+    <t>TC_Audit_18</t>
+  </si>
+  <si>
+    <t>dash_search_audit_task</t>
+  </si>
+  <si>
+    <t>Verify that Dashboard Audit Searched  Successfully</t>
+  </si>
+  <si>
+    <t>dash_view_column_headers</t>
+  </si>
+  <si>
+    <t>TC_Audit_19</t>
+  </si>
+  <si>
+    <t>show_audit_assignment</t>
+  </si>
+  <si>
+    <t>not_show_audit_assignment</t>
+  </si>
+  <si>
+    <t>TC_Audit_20</t>
+  </si>
+  <si>
+    <t>Verify that an assignment can be created successfully for not show assign checklist to sub auditee</t>
+  </si>
+  <si>
+    <t>show_assign_questionnaire</t>
+  </si>
+  <si>
+    <t>show_assign_checklist</t>
+  </si>
+  <si>
+    <t>not_show_assign_questionnaire</t>
+  </si>
+  <si>
+    <t>not_show_assign_checklist</t>
+  </si>
+  <si>
+    <t>Verify that Assign Questionnaire to Sub Auditee for Questionnaire</t>
+  </si>
+  <si>
+    <t>Verify that Assign Checklist to Sub Auditee for Checklist</t>
+  </si>
+  <si>
+    <t>{"email_id" : "bhavani+69@secmark.in", "tm_user": "bhavani+89@secmark.in", "tm_pswd": "Bhavani@123"}</t>
+  </si>
+  <si>
+    <t>{"email_head" : "bhavani+71@secmark.in", "email_subauditee1": "bhavani+89@secmark.in", "email_subauditee2":"bhavani+69@secmark.in", "tm_user":"bhavani+89@secmark.in", "tm_pswd":"Bhavani@123"}</t>
   </si>
 </sst>
 </file>
@@ -3604,7 +3667,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3961,6 +4024,9 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6693,7 +6759,7 @@
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B2" s="41" t="s">
         <v>339</v>
@@ -11133,11 +11199,11 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="93" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="38.42578125" bestFit="1" customWidth="1"/>
@@ -11172,13 +11238,13 @@
         <v>946</v>
       </c>
       <c r="C2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D2" s="82" t="s">
         <v>272</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="F2" s="66" t="s">
         <v>134</v>
@@ -11192,7 +11258,7 @@
         <v>949</v>
       </c>
       <c r="C3" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D3" s="82" t="s">
         <v>272</v>
@@ -11207,10 +11273,10 @@
         <v>950</v>
       </c>
       <c r="B4" s="82" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D4" s="82" t="s">
         <v>272</v>
@@ -11228,7 +11294,7 @@
         <v>952</v>
       </c>
       <c r="C5" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D5" s="82" t="s">
         <v>272</v>
@@ -11246,7 +11312,7 @@
         <v>953</v>
       </c>
       <c r="C6" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="D6" s="120" t="s">
         <v>272</v>
@@ -11263,7 +11329,7 @@
         <v>956</v>
       </c>
       <c r="C7" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="D7" s="120" t="s">
         <v>272</v>
@@ -11280,7 +11346,7 @@
         <v>958</v>
       </c>
       <c r="C8" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D8" s="120" t="s">
         <v>272</v>
@@ -11297,7 +11363,7 @@
         <v>960</v>
       </c>
       <c r="C9" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D9" s="120" t="s">
         <v>272</v>
@@ -11314,7 +11380,7 @@
         <v>962</v>
       </c>
       <c r="C10" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="D10" s="120" t="s">
         <v>272</v>
@@ -11328,7 +11394,7 @@
         <v>963</v>
       </c>
       <c r="B11" s="120" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C11" t="s">
         <v>978</v>
@@ -11336,19 +11402,16 @@
       <c r="D11" s="120" t="s">
         <v>272</v>
       </c>
-      <c r="E11" t="s">
-        <v>992</v>
-      </c>
       <c r="F11" s="120" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="47" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B12" s="120" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C12" t="s">
         <v>979</v>
@@ -11362,13 +11425,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="47" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B13" s="120" t="s">
-        <v>968</v>
+        <v>982</v>
       </c>
       <c r="C13" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="D13" s="120" t="s">
         <v>272</v>
@@ -11378,14 +11441,14 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="47" t="s">
-        <v>982</v>
+      <c r="A14" s="115" t="s">
+        <v>981</v>
       </c>
       <c r="B14" s="120" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C14" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="D14" s="120" t="s">
         <v>272</v>
@@ -11395,40 +11458,174 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="115" t="s">
-        <v>985</v>
+      <c r="A15" s="47" t="s">
+        <v>984</v>
       </c>
       <c r="B15" s="120" t="s">
-        <v>986</v>
+        <v>1002</v>
       </c>
       <c r="C15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="D15" s="120" t="s">
         <v>272</v>
       </c>
+      <c r="E15" t="s">
+        <v>990</v>
+      </c>
       <c r="F15" s="120" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="115" t="s">
+        <v>987</v>
+      </c>
+      <c r="B16" s="120" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C16" t="s">
         <v>988</v>
-      </c>
-      <c r="B16" s="120" t="s">
-        <v>990</v>
-      </c>
-      <c r="C16" t="s">
-        <v>989</v>
       </c>
       <c r="D16" s="120" t="s">
         <v>272</v>
       </c>
-      <c r="E16" s="47" t="s">
-        <v>991</v>
+      <c r="E16" s="62" t="s">
+        <v>1012</v>
       </c>
       <c r="F16" s="120" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A17" s="115" t="s">
+        <v>991</v>
+      </c>
+      <c r="B17" s="120" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C17" t="s">
+        <v>992</v>
+      </c>
+      <c r="D17" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="E17" s="108" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F17" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="115" t="s">
+        <v>995</v>
+      </c>
+      <c r="B18" s="120" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D18" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="E18" s="108" t="s">
+        <v>990</v>
+      </c>
+      <c r="F18" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="115" t="s">
+        <v>997</v>
+      </c>
+      <c r="B19" s="120" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D19" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="E19" s="108" t="s">
+        <v>989</v>
+      </c>
+      <c r="F19" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="A20" s="115" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B20" s="120" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D20" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="E20" s="108" t="s">
+        <v>993</v>
+      </c>
+      <c r="F20" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="115" t="s">
+        <v>997</v>
+      </c>
+      <c r="B21" s="120" t="s">
+        <v>994</v>
+      </c>
+      <c r="C21" t="s">
+        <v>996</v>
+      </c>
+      <c r="D21" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="F21" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="115" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B22" s="120" t="s">
+        <v>998</v>
+      </c>
+      <c r="C22" t="s">
+        <v>999</v>
+      </c>
+      <c r="D22" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="F22" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="115" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B23" s="120" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C23" t="s">
+        <v>972</v>
+      </c>
+      <c r="D23" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="F23" s="120" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -11447,7 +11644,8 @@
   <cols>
     <col min="1" max="1" width="16.140625" style="22" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.7109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" style="23" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" style="22" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="93.28515625" style="22" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="42.7109375" style="22" bestFit="1" customWidth="1"/>
@@ -11545,10 +11743,10 @@
       <c r="B2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="145">
         <v>45876</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="145">
         <v>45879</v>
       </c>
       <c r="E2" s="12" t="s">
@@ -11606,10 +11804,10 @@
       <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="145">
         <v>45876</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="145">
         <v>45879</v>
       </c>
       <c r="E3" s="12" t="s">
@@ -11669,10 +11867,10 @@
       <c r="B4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="145">
         <v>45876</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="145">
         <v>45873</v>
       </c>
       <c r="E4" s="12" t="s">
@@ -11732,10 +11930,10 @@
       <c r="B5" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="145">
         <v>45868</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="145">
         <v>45870</v>
       </c>
       <c r="E5" s="12" t="s">
@@ -11795,8 +11993,8 @@
       <c r="B6" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10">
+      <c r="C6" s="145"/>
+      <c r="D6" s="145">
         <v>45873</v>
       </c>
       <c r="E6" s="12" t="s">
@@ -11856,10 +12054,10 @@
       <c r="B7" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="145">
         <v>45876</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="145">
         <v>45868</v>
       </c>
       <c r="E7" s="12" t="s">
@@ -11919,10 +12117,10 @@
       <c r="B8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="145">
         <v>45876</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="145">
         <v>45871</v>
       </c>
       <c r="E8" s="12" t="s">
@@ -11982,10 +12180,10 @@
       <c r="B9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="145">
         <v>45876</v>
       </c>
-      <c r="D9" s="11"/>
+      <c r="D9" s="145"/>
       <c r="E9" s="12" t="s">
         <v>25</v>
       </c>
@@ -12043,10 +12241,10 @@
       <c r="B10" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="145">
         <v>45876</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="145">
         <v>45879</v>
       </c>
       <c r="E10" s="10"/>
@@ -12104,10 +12302,10 @@
       <c r="B11" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="145">
         <v>45876</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="145">
         <v>45879</v>
       </c>
       <c r="E11" s="12" t="s">
@@ -12167,10 +12365,10 @@
       <c r="B12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="145">
         <v>45876</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="145">
         <v>45876</v>
       </c>
       <c r="E12" s="12" t="s">
@@ -12226,10 +12424,10 @@
       <c r="B13" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="145">
         <v>45876</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="145">
         <v>45879</v>
       </c>
       <c r="E13" s="12" t="s">
@@ -12287,10 +12485,10 @@
       <c r="B14" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="145">
         <v>45876</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="145">
         <v>45879</v>
       </c>
       <c r="E14" s="12" t="s">
@@ -12346,10 +12544,10 @@
       <c r="B15" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="145">
         <v>45876</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="145">
         <v>45879</v>
       </c>
       <c r="E15" s="12" t="s">
@@ -12405,10 +12603,10 @@
       <c r="B16" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="145">
         <v>45876</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="145">
         <v>45879</v>
       </c>
       <c r="E16" s="12" t="s">
@@ -12464,10 +12662,10 @@
       <c r="B17" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="145">
         <v>45876</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="145">
         <v>45879</v>
       </c>
       <c r="E17" s="12" t="s">
@@ -12523,10 +12721,10 @@
       <c r="B18" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="145">
         <v>45876</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="145">
         <v>45879</v>
       </c>
       <c r="E18" s="12" t="s">
@@ -12582,10 +12780,10 @@
       <c r="B19" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="145">
         <v>45876</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="145">
         <v>45879</v>
       </c>
       <c r="E19" s="12" t="s">
@@ -12641,10 +12839,10 @@
       <c r="B20" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="145">
         <v>45876</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="145">
         <v>45879</v>
       </c>
       <c r="E20" s="12" t="s">
@@ -12698,10 +12896,10 @@
       <c r="B21" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="145">
         <v>45876</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="145">
         <v>45879</v>
       </c>
       <c r="E21" s="12" t="s">
@@ -12755,10 +12953,10 @@
       <c r="B22" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="145">
         <v>45876</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="145">
         <v>45879</v>
       </c>
       <c r="E22" s="12" t="s">

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" firstSheet="19" activeTab="21"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" firstSheet="7" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="credentials" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="1014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2983" uniqueCount="1015">
   <si>
     <t>task_name</t>
   </si>
@@ -2918,9 +2918,6 @@
     <t>search_company_name</t>
   </si>
   <si>
-    <t>view_column_headers</t>
-  </si>
-  <si>
     <t>TC_Audit_5</t>
   </si>
   <si>
@@ -3099,6 +3096,12 @@
   </si>
   <si>
     <t>{"email_head" : "bhavani+71@secmark.in", "email_subauditee1": "bhavani+89@secmark.in", "email_subauditee2":"bhavani+69@secmark.in", "tm_user":"bhavani+89@secmark.in", "tm_pswd":"Bhavani@123"}</t>
+  </si>
+  <si>
+    <t>company_column_headers</t>
+  </si>
+  <si>
+    <t>{"email_id" : "bhavani+71@secmark.in"}</t>
   </si>
 </sst>
 </file>
@@ -6759,7 +6762,7 @@
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B2" s="41" t="s">
         <v>339</v>
@@ -6878,7 +6881,7 @@
       </c>
       <c r="E4" s="62"/>
       <c r="F4" s="66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.25">
@@ -7094,7 +7097,7 @@
       </c>
       <c r="E16" s="62"/>
       <c r="F16" s="120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.25">
@@ -7112,7 +7115,7 @@
       </c>
       <c r="E17" s="62"/>
       <c r="F17" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.25">
@@ -7130,7 +7133,7 @@
       </c>
       <c r="E18" s="62"/>
       <c r="F18" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.25">
@@ -7148,7 +7151,7 @@
       </c>
       <c r="E19" s="62"/>
       <c r="F19" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.25">
@@ -7166,7 +7169,7 @@
       </c>
       <c r="E20" s="62"/>
       <c r="F20" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.25">
@@ -10441,7 +10444,7 @@
         <v>128</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C8" s="44" t="s">
         <v>133</v>
@@ -10623,7 +10626,7 @@
         <v>945</v>
       </c>
       <c r="B21" s="144" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C21" s="144" t="s">
         <v>133</v>
@@ -11238,13 +11241,13 @@
         <v>946</v>
       </c>
       <c r="C2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="D2" s="82" t="s">
         <v>272</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F2" s="66" t="s">
         <v>134</v>
@@ -11258,14 +11261,16 @@
         <v>949</v>
       </c>
       <c r="C3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D3" s="82" t="s">
         <v>272</v>
       </c>
-      <c r="E3" s="47"/>
+      <c r="E3" s="47" t="s">
+        <v>1014</v>
+      </c>
       <c r="F3" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -11273,10 +11278,10 @@
         <v>950</v>
       </c>
       <c r="B4" s="82" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C4" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D4" s="82" t="s">
         <v>272</v>
@@ -11294,7 +11299,7 @@
         <v>952</v>
       </c>
       <c r="C5" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D5" s="82" t="s">
         <v>272</v>
@@ -11306,13 +11311,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="47" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B6" s="120" t="s">
-        <v>953</v>
+        <v>1013</v>
       </c>
       <c r="C6" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D6" s="120" t="s">
         <v>272</v>
@@ -11323,13 +11328,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B7" s="120" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="C7" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="D7" s="120" t="s">
         <v>272</v>
@@ -11340,13 +11345,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B8" s="120" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="C8" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="D8" s="120" t="s">
         <v>272</v>
@@ -11357,13 +11362,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="47" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B9" s="120" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="C9" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="D9" s="120" t="s">
         <v>272</v>
@@ -11374,13 +11379,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="47" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B10" s="120" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="C10" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="D10" s="120" t="s">
         <v>272</v>
@@ -11391,13 +11396,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B11" s="120" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="C11" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="D11" s="120" t="s">
         <v>272</v>
@@ -11408,13 +11413,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="47" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B12" s="120" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C12" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="D12" s="120" t="s">
         <v>272</v>
@@ -11425,13 +11430,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="47" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B13" s="120" t="s">
+        <v>981</v>
+      </c>
+      <c r="C13" t="s">
         <v>982</v>
-      </c>
-      <c r="C13" t="s">
-        <v>983</v>
       </c>
       <c r="D13" s="120" t="s">
         <v>272</v>
@@ -11442,13 +11447,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="115" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B14" s="120" t="s">
+        <v>984</v>
+      </c>
+      <c r="C14" t="s">
         <v>985</v>
-      </c>
-      <c r="C14" t="s">
-        <v>986</v>
       </c>
       <c r="D14" s="120" t="s">
         <v>272</v>
@@ -11459,19 +11464,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="47" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B15" s="120" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C15" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D15" s="120" t="s">
         <v>272</v>
       </c>
       <c r="E15" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F15" s="120" t="s">
         <v>134</v>
@@ -11479,39 +11484,39 @@
     </row>
     <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="115" t="s">
+        <v>986</v>
+      </c>
+      <c r="B16" s="120" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C16" t="s">
         <v>987</v>
-      </c>
-      <c r="B16" s="120" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C16" t="s">
-        <v>988</v>
       </c>
       <c r="D16" s="120" t="s">
         <v>272</v>
       </c>
       <c r="E16" s="62" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="F16" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A17" s="115" t="s">
+        <v>990</v>
+      </c>
+      <c r="B17" s="120" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C17" t="s">
         <v>991</v>
-      </c>
-      <c r="B17" s="120" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C17" t="s">
-        <v>992</v>
       </c>
       <c r="D17" s="120" t="s">
         <v>272</v>
       </c>
       <c r="E17" s="108" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="F17" s="120" t="s">
         <v>134</v>
@@ -11519,19 +11524,19 @@
     </row>
     <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="115" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B18" s="120" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C18" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D18" s="120" t="s">
         <v>272</v>
       </c>
       <c r="E18" s="108" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F18" s="120" t="s">
         <v>134</v>
@@ -11539,19 +11544,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="115" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B19" s="120" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C19" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="D19" s="120" t="s">
         <v>272</v>
       </c>
       <c r="E19" s="108" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F19" s="120" t="s">
         <v>134</v>
@@ -11559,19 +11564,19 @@
     </row>
     <row r="20" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="115" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B20" s="120" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C20" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="D20" s="120" t="s">
         <v>272</v>
       </c>
       <c r="E20" s="108" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F20" s="120" t="s">
         <v>134</v>
@@ -11579,13 +11584,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="115" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B21" s="120" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C21" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D21" s="120" t="s">
         <v>272</v>
@@ -11596,13 +11601,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="115" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B22" s="120" t="s">
+        <v>997</v>
+      </c>
+      <c r="C22" t="s">
         <v>998</v>
-      </c>
-      <c r="C22" t="s">
-        <v>999</v>
       </c>
       <c r="D22" s="120" t="s">
         <v>272</v>
@@ -11613,13 +11618,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="115" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B23" s="120" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C23" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D23" s="120" t="s">
         <v>272</v>
